--- a/METAS 2026.xlsx
+++ b/METAS 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoequatorialenergia-my.sharepoint.com/personal/suene_silva_equatorialenergia_com_br/Documents/SUENE MARQUES/SITE PRODUÇÃO 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11417170-F61A-4D10-A07B-3C3DC6DE4552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{11417170-F61A-4D10-A07B-3C3DC6DE4552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30313DF4-AF00-4EA4-A241-4E415D530A85}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="624" windowWidth="23256" windowHeight="12456" xr2:uid="{782DD64E-CD9D-4905-9FBE-C3B5A61A20CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{782DD64E-CD9D-4905-9FBE-C3B5A61A20CB}"/>
   </bookViews>
   <sheets>
     <sheet name="METAS 2026" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="52">
   <si>
     <t>REGIONAL</t>
   </si>
@@ -203,7 +203,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -251,7 +251,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E620BDAC-D28A-48E1-BFB8-FB1F84880F87}">
-  <dimension ref="A1:E685"/>
+  <dimension ref="A1:E697"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
@@ -12239,6 +12239,210 @@
         <v>49</v>
       </c>
     </row>
+    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A686" s="2">
+        <v>18352.779038004752</v>
+      </c>
+      <c r="B686" t="s">
+        <v>32</v>
+      </c>
+      <c r="C686" t="s">
+        <v>4</v>
+      </c>
+      <c r="D686" t="s">
+        <v>16</v>
+      </c>
+      <c r="E686" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A687" s="2">
+        <v>19072.495863024546</v>
+      </c>
+      <c r="B687" t="s">
+        <v>32</v>
+      </c>
+      <c r="C687" t="s">
+        <v>5</v>
+      </c>
+      <c r="D687" t="s">
+        <v>16</v>
+      </c>
+      <c r="E687" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A688" s="2">
+        <v>21591.504750593824</v>
+      </c>
+      <c r="B688" t="s">
+        <v>32</v>
+      </c>
+      <c r="C688" t="s">
+        <v>6</v>
+      </c>
+      <c r="D688" t="s">
+        <v>16</v>
+      </c>
+      <c r="E688" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A689" s="2">
+        <v>19792.212688044339</v>
+      </c>
+      <c r="B689" t="s">
+        <v>32</v>
+      </c>
+      <c r="C689" t="s">
+        <v>7</v>
+      </c>
+      <c r="D689" t="s">
+        <v>16</v>
+      </c>
+      <c r="E689" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A690" s="2">
+        <v>20511.929513064137</v>
+      </c>
+      <c r="B690" t="s">
+        <v>32</v>
+      </c>
+      <c r="C690" t="s">
+        <v>8</v>
+      </c>
+      <c r="D690" t="s">
+        <v>16</v>
+      </c>
+      <c r="E690" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A691" s="2">
+        <v>21591.504750593824</v>
+      </c>
+      <c r="B691" t="s">
+        <v>32</v>
+      </c>
+      <c r="C691" t="s">
+        <v>9</v>
+      </c>
+      <c r="D691" t="s">
+        <v>16</v>
+      </c>
+      <c r="E691" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A692" s="2">
+        <v>22671.079988123514</v>
+      </c>
+      <c r="B692" t="s">
+        <v>32</v>
+      </c>
+      <c r="C692" t="s">
+        <v>10</v>
+      </c>
+      <c r="D692" t="s">
+        <v>16</v>
+      </c>
+      <c r="E692" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A693" s="2">
+        <v>21231.64633808393</v>
+      </c>
+      <c r="B693" t="s">
+        <v>32</v>
+      </c>
+      <c r="C693" t="s">
+        <v>11</v>
+      </c>
+      <c r="D693" t="s">
+        <v>16</v>
+      </c>
+      <c r="E693" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A694" s="2">
+        <v>20511.929513064133</v>
+      </c>
+      <c r="B694" t="s">
+        <v>32</v>
+      </c>
+      <c r="C694" t="s">
+        <v>12</v>
+      </c>
+      <c r="D694" t="s">
+        <v>16</v>
+      </c>
+      <c r="E694" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A695" s="2">
+        <v>19432.354275534442</v>
+      </c>
+      <c r="B695" t="s">
+        <v>32</v>
+      </c>
+      <c r="C695" t="s">
+        <v>13</v>
+      </c>
+      <c r="D695" t="s">
+        <v>16</v>
+      </c>
+      <c r="E695" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A696" s="2">
+        <v>16553.486975455267</v>
+      </c>
+      <c r="B696" t="s">
+        <v>32</v>
+      </c>
+      <c r="C696" t="s">
+        <v>14</v>
+      </c>
+      <c r="D696" t="s">
+        <v>16</v>
+      </c>
+      <c r="E696" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A697" s="2">
+        <v>18712.637450514649</v>
+      </c>
+      <c r="B697" t="s">
+        <v>32</v>
+      </c>
+      <c r="C697" t="s">
+        <v>15</v>
+      </c>
+      <c r="D697" t="s">
+        <v>16</v>
+      </c>
+      <c r="E697" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/METAS 2026.xlsx
+++ b/METAS 2026.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoequatorialenergia-my.sharepoint.com/personal/suene_silva_equatorialenergia_com_br/Documents/SUENE MARQUES/SITE PRODUÇÃO 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{11417170-F61A-4D10-A07B-3C3DC6DE4552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30313DF4-AF00-4EA4-A241-4E415D530A85}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{11417170-F61A-4D10-A07B-3C3DC6DE4552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C5923A3-44CA-4CFD-8A8F-CC35446773F3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{782DD64E-CD9D-4905-9FBE-C3B5A61A20CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{782DD64E-CD9D-4905-9FBE-C3B5A61A20CB}"/>
   </bookViews>
   <sheets>
     <sheet name="METAS 2026" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'METAS 2026'!$A$1:$E$697</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -590,8 +593,11 @@
   <dimension ref="A1:E697"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12241,7 +12247,7 @@
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A686" s="2">
-        <v>18352.779038004752</v>
+        <v>15730.95346114693</v>
       </c>
       <c r="B686" t="s">
         <v>32</v>
@@ -12258,7 +12264,7 @@
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" s="2">
-        <v>19072.495863024546</v>
+        <v>16347.853596878182</v>
       </c>
       <c r="B687" t="s">
         <v>32</v>
@@ -12275,7 +12281,7 @@
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" s="2">
-        <v>21591.504750593824</v>
+        <v>18507.004071937565</v>
       </c>
       <c r="B688" t="s">
         <v>32</v>
@@ -12292,7 +12298,7 @@
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" s="2">
-        <v>19792.212688044339</v>
+        <v>16964.753732609435</v>
       </c>
       <c r="B689" t="s">
         <v>32</v>
@@ -12309,7 +12315,7 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" s="2">
-        <v>20511.929513064137</v>
+        <v>17581.653868340687</v>
       </c>
       <c r="B690" t="s">
         <v>32</v>
@@ -12326,7 +12332,7 @@
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" s="2">
-        <v>21591.504750593824</v>
+        <v>18507.004071937565</v>
       </c>
       <c r="B691" t="s">
         <v>32</v>
@@ -12343,7 +12349,7 @@
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" s="2">
-        <v>22671.079988123514</v>
+        <v>19432.354275534442</v>
       </c>
       <c r="B692" t="s">
         <v>32</v>
@@ -12360,7 +12366,7 @@
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" s="2">
-        <v>21231.64633808393</v>
+        <v>18198.554004071939</v>
       </c>
       <c r="B693" t="s">
         <v>32</v>
@@ -12377,7 +12383,7 @@
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694" s="2">
-        <v>20511.929513064133</v>
+        <v>17581.653868340687</v>
       </c>
       <c r="B694" t="s">
         <v>32</v>
@@ -12394,7 +12400,7 @@
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695" s="2">
-        <v>19432.354275534442</v>
+        <v>16656.303664743809</v>
       </c>
       <c r="B695" t="s">
         <v>32</v>
@@ -12411,7 +12417,7 @@
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" s="2">
-        <v>16553.486975455267</v>
+        <v>14188.7031218188</v>
       </c>
       <c r="B696" t="s">
         <v>32</v>
@@ -12428,7 +12434,7 @@
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697" s="2">
-        <v>18712.637450514649</v>
+        <v>16039.403529012556</v>
       </c>
       <c r="B697" t="s">
         <v>32</v>
@@ -12444,6 +12450,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E697" xr:uid="{E620BDAC-D28A-48E1-BFB8-FB1F84880F87}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
